--- a/Autonomous_Driving_Task_Division.xlsx
+++ b/Autonomous_Driving_Task_Division.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aliad\Desktop\Universty\prototyping\Prototyping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{829440A0-9AC4-4329-ADE1-15F00A47B845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD53B01E-5476-42E9-842A-62566C782791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>Autonomous Driving Project – Team Task Division</t>
   </si>
@@ -55,42 +55,21 @@
     <t>Obstacle Detection</t>
   </si>
   <si>
-    <t>Detect and avoid obstacles</t>
-  </si>
-  <si>
-    <t>Speed Optimization</t>
-  </si>
-  <si>
-    <t>Improve vehicle performance</t>
-  </si>
-  <si>
     <t>Routing Functions</t>
   </si>
   <si>
     <t>Oval and figure-eight routing</t>
   </si>
   <si>
-    <t>Parking Function</t>
-  </si>
-  <si>
     <t>Autonomous parking capability</t>
   </si>
   <si>
-    <t>Milestone 1</t>
-  </si>
-  <si>
-    <t>Vehicle follows lane successfully</t>
-  </si>
-  <si>
     <t>Milestone 2</t>
   </si>
   <si>
     <t>Vehicle detects obstacles successfully</t>
   </si>
   <si>
-    <t>Create Use case diagaram, Activity diagram and Package diagram</t>
-  </si>
-  <si>
     <t xml:space="preserve">Prototype Simulation </t>
   </si>
   <si>
@@ -115,10 +94,59 @@
     <t xml:space="preserve">Organized the files for the first meeting </t>
   </si>
   <si>
-    <t>Create Requirements diagaram and Internal Block Diagram (IBD)</t>
-  </si>
-  <si>
-    <t>Create Sequence diagaram and Block Definition Diagram (BDD)</t>
+    <t>Created Requirements diagaram and Internal Block Diagram (IBD)</t>
+  </si>
+  <si>
+    <t>Created Use case diagaram, Activity diagram and Package diagram</t>
+  </si>
+  <si>
+    <t>Created Sequence diagaram and Block Definition Diagram (BDD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Created TinkerCad simulation circuit (with coding for detecting the line only) and electrical circuit </t>
+  </si>
+  <si>
+    <t>Performed cable management and wire routing, organized and assembled components, optimized the code to suit the available hardware conditions, implemented black line detection and tracking, calibrated IR sensors, integrated system components, Speed Optimization and Performance Tuning for Improved Line-Tracking Accuracy and Stability and conducted real-world testing and performance evaluation of the car.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detect and avoid obstacles </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Milestone 1</t>
+    </r>
+  </si>
+  <si>
+    <t>The Vehicle Should follows the line</t>
+  </si>
+  <si>
+    <t>Autonomous parking was excluded from the final implementation. Instead, after detecting the second obstacle, the vehicle performs a 180° turn, reacquires the line, and continues autonomous line following.</t>
+  </si>
+  <si>
+    <t>Parking Function,180° Turn and Line Reacquisition (BONUS)</t>
+  </si>
+  <si>
+    <t>Achived and the car was able to follow the black line smoothly without any issues</t>
+  </si>
+  <si>
+    <t>Optimized differential motor control, turning behavior, speed parameters, and sensor response to achieve smoother movement, more reliable curve tracking, and stable autonomous operation.</t>
+  </si>
+  <si>
+    <t>Integrated and calibrated the ultrasonic sensors, developed the obstacle-detection and state-based avoidance logic, optimized maneuver timing and motor speeds, and tested the complete sequence of obstacle detection, avoidance, line reacquisition, and continued line following.</t>
+  </si>
+  <si>
+    <t>Successfully validated the integrated system: the vehicle follows the line, detects and avoids the first obstacle, reacquires the line, responds to the second obstacle with a 180° turn, and continues autonomous line following.</t>
   </si>
 </sst>
 </file>
@@ -161,7 +189,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -183,8 +211,26 @@
         <fgColor rgb="FFDCE6F1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -207,11 +253,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -231,10 +314,61 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -537,7 +671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.5703125" customWidth="1"/>
@@ -545,26 +679,26 @@
     <col min="3" max="3" width="46.42578125" customWidth="1"/>
     <col min="4" max="4" width="28.85546875" customWidth="1"/>
     <col min="5" max="5" width="27.85546875" customWidth="1"/>
-    <col min="6" max="6" width="36.42578125" customWidth="1"/>
+    <col min="6" max="6" width="39.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
     </row>
     <row r="4" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -577,13 +711,13 @@
         <v>3</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -597,13 +731,13 @@
         <v>5</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -617,131 +751,137 @@
         <v>7</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="E7" s="7" t="s">
+        <v>27</v>
+      </c>
       <c r="F7" s="2"/>
     </row>
-    <row r="8" spans="1:6" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+    </row>
+    <row r="9" spans="1:6" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10">
+        <v>5</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="20"/>
+      <c r="F9" s="21"/>
+    </row>
+    <row r="10" spans="1:6" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="8">
+        <v>6</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" spans="1:6" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <v>5</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:6" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
-        <v>6</v>
-      </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
+      <c r="D10" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="23"/>
+      <c r="F10" s="24"/>
     </row>
     <row r="11" spans="1:6" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>7</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
+      <c r="B11" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="17"/>
+      <c r="F11" s="18"/>
     </row>
     <row r="12" spans="1:6" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
+      <c r="A12" s="8">
         <v>8</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
+      <c r="B12" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="23"/>
+      <c r="F12" s="24"/>
     </row>
     <row r="13" spans="1:6" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>9</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:6" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
-        <v>10</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-    </row>
-    <row r="15" spans="1:6" ht="54.95" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B13" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="17"/>
+      <c r="F13" s="18"/>
+    </row>
+    <row r="14" spans="1:6" ht="54.95" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="7">
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="D13:F13"/>
     <mergeCell ref="A1:F2"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D10:F10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup scale="70" orientation="landscape" r:id="rId1"/>
